--- a/Knowledge/Model Schema/CELH/Model Output/CELH_test.xlsx
+++ b/Knowledge/Model Schema/CELH/Model Output/CELH_test.xlsx
@@ -3886,7 +3886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3895,29 +3895,25 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr"/>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Q3 FY2022</t>
+          <t>Q2 FY2022</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>Q1 FY2023</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>Q2 FY2023</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Q3 FY2023</t>
-        </is>
-      </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Q1 FY2024</t>
@@ -3926,26 +3922,6 @@
       <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Q2 FY2024</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Q3 FY2024</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Q1 FY2025</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>Q2 FY2025</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>Q3 FY2025</t>
         </is>
       </c>
     </row>
@@ -3956,13 +3932,13 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>475640</v>
+        <v>287408</v>
       </c>
       <c r="C2" s="4" t="n">
+        <v>259939</v>
+      </c>
+      <c r="D2" s="4" t="n">
         <v>585822</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>970579</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>355708</v>
@@ -3970,18 +3946,6 @@
       <c r="F2" s="4" t="n">
         <v>757685</v>
       </c>
-      <c r="G2" s="4" t="n">
-        <v>1023433</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>329276</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>1068535</v>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>1793641</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -3990,13 +3954,13 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>-283778</v>
+        <v>-174195</v>
       </c>
       <c r="C3" s="4" t="n">
+        <v>-146121</v>
+      </c>
+      <c r="D3" s="4" t="n">
         <v>-313010</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>-503685</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>-173501</v>
@@ -4004,18 +3968,6 @@
       <c r="F3" s="4" t="n">
         <v>-366380</v>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>-509899</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>-156903</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>-515311</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>-868138</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -4043,22 +3995,6 @@
         <f>F2+F3</f>
         <v/>
       </c>
-      <c r="G4" s="6">
-        <f>G2+G3</f>
-        <v/>
-      </c>
-      <c r="H4" s="6">
-        <f>H2+H3</f>
-        <v/>
-      </c>
-      <c r="I4" s="6">
-        <f>I2+I3</f>
-        <v/>
-      </c>
-      <c r="J4" s="6">
-        <f>J2+J3</f>
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -4067,13 +4003,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>-316917</v>
+        <v>-90667</v>
       </c>
       <c r="C5" s="4" t="n">
+        <v>-68905</v>
+      </c>
+      <c r="D5" s="4" t="n">
         <v>-163086</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>-259471</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>-99017</v>
@@ -4081,452 +4017,240 @@
       <c r="F5" s="4" t="n">
         <v>-213867</v>
       </c>
-      <c r="G5" s="4" t="n">
-        <v>-339310</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>-120342</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>-358228</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>-563799</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Distributor Termination Fees</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>246707</v>
+          <t>Income (Loss) from Operations</t>
+        </is>
+      </c>
+      <c r="B6" s="6">
+        <f>B4+B5</f>
+        <v/>
+      </c>
+      <c r="C6" s="6">
+        <f>C4+C5</f>
+        <v/>
+      </c>
+      <c r="D6" s="6">
+        <f>D4+D5</f>
+        <v/>
+      </c>
+      <c r="E6" s="6">
+        <f>E4+E5</f>
+        <v/>
+      </c>
+      <c r="F6" s="6">
+        <f>F4+F5</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Income (Loss) from Operations</t>
-        </is>
-      </c>
-      <c r="B7" s="6">
-        <f>B4+SUM(B5:B6)</f>
-        <v/>
-      </c>
-      <c r="C7" s="6">
-        <f>C4+SUM(C5:C6)</f>
-        <v/>
-      </c>
-      <c r="D7" s="6">
-        <f>D4+SUM(D5:D6)</f>
-        <v/>
-      </c>
-      <c r="E7" s="6">
-        <f>E4+SUM(E5:E6)</f>
-        <v/>
-      </c>
-      <c r="F7" s="6">
-        <f>F4+SUM(F5:F6)</f>
-        <v/>
-      </c>
-      <c r="G7" s="6">
-        <f>G4+SUM(G5:G6)</f>
-        <v/>
-      </c>
-      <c r="H7" s="6">
-        <f>H4+SUM(H5:H6)</f>
-        <v/>
-      </c>
-      <c r="I7" s="6">
-        <f>I4+SUM(I5:I6)</f>
-        <v/>
-      </c>
-      <c r="J7" s="6">
-        <f>J4+SUM(J5:J6)</f>
-        <v/>
+          <t>Interest Income (Expense)</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>129</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>4969</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>10542</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>9640</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>20287</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Interest Income (Expense)</t>
+          <t>Foreign Currency Gain (Loss)</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>1579</v>
+        <v>-676</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>10542</v>
+        <v>-118</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>17767</v>
+        <v>-1049</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>9612</v>
+        <v>-369</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>20287</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>31399</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>7846</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>-6196</v>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>-19592</v>
+        <v>-633</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Foreign Currency Gain (Loss)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
-        <v>-930</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>-1049</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>-1226</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>-633</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>-356</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>0</v>
+          <t>Pre-Tax Income (Loss)</t>
+        </is>
+      </c>
+      <c r="B9" s="6">
+        <f>B6+SUM(B7:B8)</f>
+        <v/>
+      </c>
+      <c r="C9" s="6">
+        <f>C6+SUM(C7:C8)</f>
+        <v/>
+      </c>
+      <c r="D9" s="6">
+        <f>D6+SUM(D7:D8)</f>
+        <v/>
+      </c>
+      <c r="E9" s="6">
+        <f>E6+SUM(E7:E8)</f>
+        <v/>
+      </c>
+      <c r="F9" s="6">
+        <f>F6+SUM(F7:F8)</f>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Other Income (Expense)</t>
+          <t>Income Tax (Expense) Benefit</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>0</v>
+        <v>-6161</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0</v>
+        <v>-8537</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0</v>
+        <v>-26483</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-341</v>
+        <v>-14650</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>1116</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>1658</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>7022</v>
+        <v>-39498</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Pre-Tax Income (Loss)</t>
+          <t>Net Income (Loss)</t>
         </is>
       </c>
       <c r="B11" s="6">
-        <f>B7+SUM(B8:B10)</f>
+        <f>B9+B10</f>
         <v/>
       </c>
       <c r="C11" s="6">
-        <f>C7+SUM(C8:C10)</f>
+        <f>C9+C10</f>
         <v/>
       </c>
       <c r="D11" s="6">
-        <f>D7+SUM(D8:D10)</f>
+        <f>D9+D10</f>
         <v/>
       </c>
       <c r="E11" s="6">
-        <f>E7+SUM(E8:E10)</f>
+        <f>E9+E10</f>
         <v/>
       </c>
       <c r="F11" s="6">
-        <f>F7+SUM(F8:F10)</f>
-        <v/>
-      </c>
-      <c r="G11" s="6">
-        <f>G7+SUM(G8:G10)</f>
-        <v/>
-      </c>
-      <c r="H11" s="6">
-        <f>H7+SUM(H8:H10)</f>
-        <v/>
-      </c>
-      <c r="I11" s="6">
-        <f>I7+SUM(I8:I10)</f>
-        <v/>
-      </c>
-      <c r="J11" s="6">
-        <f>J7+SUM(J8:J10)</f>
+        <f>F9+F10</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Income Tax (Expense) Benefit</t>
+          <t>Net Income (Loss) Less NCI</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>-41653</v>
+        <v>15838</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-26483</v>
+        <v>41227</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-47279</v>
+        <v>92736</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-14650</v>
+        <v>77811</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-39498</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>-41317</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>-16574</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>-46184</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>-19167</v>
+        <v>157594</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Net Income (Loss)</t>
-        </is>
-      </c>
-      <c r="B13" s="6">
-        <f>B11+B12</f>
-        <v/>
-      </c>
-      <c r="C13" s="6">
-        <f>C11+C12</f>
-        <v/>
-      </c>
-      <c r="D13" s="6">
-        <f>D11+D12</f>
-        <v/>
-      </c>
-      <c r="E13" s="6">
-        <f>E11+E12</f>
-        <v/>
-      </c>
-      <c r="F13" s="6">
-        <f>F11+F12</f>
-        <v/>
-      </c>
-      <c r="G13" s="6">
-        <f>G11+G12</f>
-        <v/>
-      </c>
-      <c r="H13" s="6">
-        <f>H11+H12</f>
-        <v/>
-      </c>
-      <c r="I13" s="6">
-        <f>I11+I12</f>
-        <v/>
-      </c>
-      <c r="J13" s="6">
-        <f>J11+J12</f>
-        <v/>
+          <t>Preferred Dividends</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>-6781</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>-13637</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>-6837</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>-13675</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Net Income (Loss) Less NCI</t>
+          <t>Income Allocated to Participating Preferred</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>-166059</v>
+        <v>0</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>92736</v>
+        <v>2934</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>176685</v>
+        <v>6727</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>77811</v>
+        <v>6128</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>157594</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>163950</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>44419</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>144274</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>83260</v>
+        <v>12417</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Preferred Dividends</t>
+          <t>Net Income (Loss) Attributable to Common Shareholders</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>-4596</v>
+        <v>15838</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-13637</v>
+        <v>31512</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-20512</v>
+        <v>72372</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-6837</v>
+        <v>64846</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-13675</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>-20588</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>-6781</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>-13632</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>-23289</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Income Allocated to Participating Preferred</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>6898</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>13263</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>6128</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>12417</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>12357</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>3219</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>10703</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>5272</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Net Income (Loss) Attributable to Common Shareholders</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>-170655</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>72201</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>142910</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>64846</v>
-      </c>
-      <c r="F17" s="4" t="n">
         <v>131502</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>131005</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>34419</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>119939</v>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v>54699</v>
       </c>
     </row>
   </sheetData>
@@ -4540,7 +4264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -4549,10 +4273,6 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4564,7 +4284,7 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>Q3 FY2023</t>
+          <t>Q2 FY2023</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
@@ -4574,32 +4294,12 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>Q1 FY2024</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>Q2 FY2024</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Q3 FY2024</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Q4 FY2024</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Q1 FY2025</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>Q2 FY2025</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>Q3 FY2025</t>
         </is>
       </c>
     </row>
@@ -4613,28 +4313,16 @@
         <v>614159</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>760022</v>
+        <v>681054</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>755981</v>
       </c>
       <c r="E2" s="4" t="n">
+        <v>879498</v>
+      </c>
+      <c r="F2" s="4" t="n">
         <v>903210</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>903748</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>890190</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>977285</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>615233</v>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>805955</v>
       </c>
     </row>
     <row r="3">
@@ -4658,18 +4346,6 @@
       <c r="F3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>126508</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -4681,28 +4357,16 @@
         <v>63311</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>215243</v>
+        <v>197811</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>183703</v>
       </c>
       <c r="E4" s="4" t="n">
+        <v>200117</v>
+      </c>
+      <c r="F4" s="4" t="n">
         <v>262920</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>208774</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>270342</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>256424</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>490389</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>513682</v>
       </c>
     </row>
     <row r="5">
@@ -4715,28 +4379,16 @@
         <v>2979</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>3309</v>
+        <v>3323</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>2318</v>
       </c>
       <c r="E5" s="4" t="n">
+        <v>2259</v>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>1166</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>1025</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4749,96 +4401,60 @@
         <v>173289</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>198704</v>
+        <v>152545</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>229275</v>
       </c>
       <c r="E6" s="4" t="n">
+        <v>197504</v>
+      </c>
+      <c r="F6" s="4" t="n">
         <v>180669</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>197572</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>131165</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>141159</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>230046</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>282514</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Prepaid Expenses</t>
+          <t>Deferred Other Costs - Current</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>11341</v>
+        <v>14124</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>23747</v>
+        <v>14124</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>19503</v>
+        <v>14124</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>22900</v>
+        <v>14124</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>38227</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>18759</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>22464</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>41420</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>163395</v>
+        <v>14124</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Deferred Other Costs - Current</t>
+          <t>Prepaid Expenses</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>14124</v>
+        <v>11341</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>14124</v>
+        <v>23398</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>14124</v>
+        <v>19503</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>14124</v>
+        <v>21523</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>14124</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>14124</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>14124</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>14124</v>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>49520</v>
+        <v>22900</v>
       </c>
     </row>
     <row r="9">
@@ -4867,22 +4483,6 @@
         <f>SUM(F2:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="6">
-        <f>SUM(G2:G8)</f>
-        <v/>
-      </c>
-      <c r="H9" s="6">
-        <f>SUM(H2:H8)</f>
-        <v/>
-      </c>
-      <c r="I9" s="6">
-        <f>SUM(I2:I8)</f>
-        <v/>
-      </c>
-      <c r="J9" s="6">
-        <f>SUM(J2:J8)</f>
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -4905,18 +4505,6 @@
       <c r="F10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -4928,130 +4516,82 @@
         <v>10185</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>21061</v>
+        <v>15892</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>24868</v>
       </c>
       <c r="E11" s="4" t="n">
+        <v>28350</v>
+      </c>
+      <c r="F11" s="4" t="n">
         <v>36282</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>38370</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>55602</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>58698</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>72516</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>80925</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>ROU Assets - Operating - Non-Current</t>
+          <t>Deferred Tax Assets</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>972</v>
+        <v>501</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1152</v>
+        <v>28373</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1957</v>
+        <v>29518</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1507</v>
+        <v>22437</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5506</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>21606</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>20866</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>0</v>
+        <v>22727</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
+          <t>ROU Assets - Operating - Non-Current</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>12254</v>
+        <v>972</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>11772</v>
+        <v>756</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>12139</v>
+        <v>1957</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>11491</v>
+        <v>1688</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>11877</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>12213</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>12444</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>1222115</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>1397819</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>ROU Assets - Finance - Non-Current</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>13679</v>
+        <v>208</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>13588</v>
+        <v>171</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>14173</v>
+        <v>208</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>13730</v>
+        <v>263</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>14360</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>71582</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>72128</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>802234</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>914957</v>
+        <v>233</v>
       </c>
     </row>
     <row r="15">
@@ -5064,96 +4604,60 @@
         <v>262462</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>251869</v>
+        <v>255400</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>248338</v>
       </c>
       <c r="E15" s="4" t="n">
+        <v>244807</v>
+      </c>
+      <c r="F15" s="4" t="n">
         <v>241276</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>237746</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>234215</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>230684</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>227153</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>784214</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Deferred Tax Assets</t>
+          <t>Intangible Assets</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>501</v>
+        <v>12254</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>30614</v>
+        <v>12211</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>29518</v>
+        <v>12139</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>22727</v>
+        <v>11741</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>24186</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>38699</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>38525</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>43158</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>110410</v>
+        <v>11491</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>ROU Assets - Finance - Non-Current</t>
+          <t>Goodwill</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>208</v>
+        <v>13679</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>148</v>
+        <v>13937</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>208</v>
+        <v>14173</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>233</v>
+        <v>13866</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>214</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v>0</v>
+        <v>13730</v>
       </c>
     </row>
     <row r="18">
@@ -5166,28 +4670,16 @@
         <v>263</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>291</v>
       </c>
       <c r="E18" s="4" t="n">
+        <v>7963</v>
+      </c>
+      <c r="F18" s="4" t="n">
         <v>6653</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>8594</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>8384</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>14717</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>36755</v>
-      </c>
-      <c r="J18" s="4" t="n">
-        <v>35809</v>
       </c>
     </row>
     <row r="19">
@@ -5216,22 +4708,6 @@
         <f>F9+SUM(F10:F18)</f>
         <v/>
       </c>
-      <c r="G19" s="6">
-        <f>G9+SUM(G10:G18)</f>
-        <v/>
-      </c>
-      <c r="H19" s="6">
-        <f>H9+SUM(H10:H18)</f>
-        <v/>
-      </c>
-      <c r="I19" s="6">
-        <f>I9+SUM(I10:I18)</f>
-        <v/>
-      </c>
-      <c r="J19" s="6">
-        <f>J9+SUM(J10:J18)</f>
-        <v/>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -5243,28 +4719,16 @@
         <v>106147</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>121088</v>
+        <v>94313</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>42840</v>
       </c>
       <c r="E20" s="4" t="n">
+        <v>40196</v>
+      </c>
+      <c r="F20" s="4" t="n">
         <v>47423</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>30938</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>41287</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>61052</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>120962</v>
-      </c>
-      <c r="J20" s="4" t="n">
-        <v>97794</v>
       </c>
     </row>
     <row r="21">
@@ -5283,22 +4747,10 @@
         <v>62120</v>
       </c>
       <c r="E21" s="4" t="n">
+        <v>63871</v>
+      </c>
+      <c r="F21" s="4" t="n">
         <v>79633</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>73024</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>148780</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>152046</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>225859</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>311768</v>
       </c>
     </row>
     <row r="22">
@@ -5311,28 +4763,16 @@
         <v>1193</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>58855</v>
+        <v>58798</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>50424</v>
       </c>
       <c r="E22" s="4" t="n">
+        <v>58619</v>
+      </c>
+      <c r="F22" s="4" t="n">
         <v>5374</v>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>739</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>10834</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>26206</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>21765</v>
-      </c>
-      <c r="J22" s="4" t="n">
-        <v>49590</v>
       </c>
     </row>
     <row r="23">
@@ -5356,18 +4796,6 @@
       <c r="F23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="4" t="n">
-        <v>252953</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -5379,28 +4807,16 @@
         <v>35977</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>136557</v>
+        <v>98933</v>
       </c>
       <c r="D24" s="4" t="n">
         <v>99787</v>
       </c>
       <c r="E24" s="4" t="n">
+        <v>129201</v>
+      </c>
+      <c r="F24" s="4" t="n">
         <v>156479</v>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>158810</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>135948</v>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>151327</v>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>200169</v>
-      </c>
-      <c r="J24" s="4" t="n">
-        <v>234068</v>
       </c>
     </row>
     <row r="25">
@@ -5413,28 +4829,16 @@
         <v>661</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>628</v>
+        <v>505</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>980</v>
       </c>
       <c r="E25" s="4" t="n">
+        <v>821</v>
+      </c>
+      <c r="F25" s="4" t="n">
         <v>729</v>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>1358</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>3265</v>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>3550</v>
-      </c>
-      <c r="I25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -5447,7 +4851,7 @@
         <v>70</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D26" s="4" t="n">
         <v>59</v>
@@ -5456,666 +4860,356 @@
         <v>61</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>99</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Contingent Consideration - Current</t>
+          <t>Deferred Revenue - Current</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>0</v>
+        <v>9675</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0</v>
+        <v>9500</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0</v>
+        <v>9513</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0</v>
+        <v>9513</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>25000</v>
-      </c>
-      <c r="J27" s="4" t="n">
-        <v>25000</v>
+        <v>9513</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Deferred Revenue - Current</t>
+          <t>Other Current Liabilities</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>9675</v>
+        <v>3586</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>9500</v>
+        <v>7109</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>9513</v>
+        <v>10890</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>9513</v>
+        <v>12987</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>9513</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>9513</v>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>9513</v>
-      </c>
-      <c r="I28" s="4" t="n">
-        <v>16071</v>
-      </c>
-      <c r="J28" s="4" t="n">
-        <v>25557</v>
+        <v>13772</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Other Current Liabilities</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>3586</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>8826</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>10890</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>13772</v>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>14979</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>15908</v>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>14160</v>
-      </c>
-      <c r="I29" s="4" t="n">
-        <v>49949</v>
-      </c>
-      <c r="J29" s="4" t="n">
-        <v>32258</v>
+          <t>Total Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B29" s="6">
+        <f>SUM(B20:B28)</f>
+        <v/>
+      </c>
+      <c r="C29" s="6">
+        <f>SUM(C20:C28)</f>
+        <v/>
+      </c>
+      <c r="D29" s="6">
+        <f>SUM(D20:D28)</f>
+        <v/>
+      </c>
+      <c r="E29" s="6">
+        <f>SUM(E20:E28)</f>
+        <v/>
+      </c>
+      <c r="F29" s="6">
+        <f>SUM(F20:F28)</f>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Total Current Liabilities</t>
-        </is>
-      </c>
-      <c r="B30" s="6">
-        <f>SUM(B20:B29)</f>
-        <v/>
-      </c>
-      <c r="C30" s="6">
-        <f>SUM(C20:C29)</f>
-        <v/>
-      </c>
-      <c r="D30" s="6">
-        <f>SUM(D20:D29)</f>
-        <v/>
-      </c>
-      <c r="E30" s="6">
-        <f>SUM(E20:E29)</f>
-        <v/>
-      </c>
-      <c r="F30" s="6">
-        <f>SUM(F20:F29)</f>
-        <v/>
-      </c>
-      <c r="G30" s="6">
-        <f>SUM(G20:G29)</f>
-        <v/>
-      </c>
-      <c r="H30" s="6">
-        <f>SUM(H20:H29)</f>
-        <v/>
-      </c>
-      <c r="I30" s="6">
-        <f>SUM(I20:I29)</f>
-        <v/>
-      </c>
-      <c r="J30" s="6">
-        <f>SUM(J20:J29)</f>
-        <v/>
+          <t>Lease Liability - Operating - Non-Current</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>326</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>249</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>955</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>850</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>762</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Lease Liability - Operating - Non-Current</t>
+          <t>Lease Liability - Finance - Non-Current</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>326</v>
+        <v>162</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>512</v>
+        <v>147</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>955</v>
+        <v>193</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>762</v>
+        <v>245</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>4193</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>16674</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>16152</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>0</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Lease Liability - Finance - Non-Current</t>
+          <t>Deferred Tax Liability</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>162</v>
+        <v>15919</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>135</v>
+        <v>2333</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>193</v>
+        <v>2880</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>228</v>
+        <v>2248</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>189</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="4" t="n">
-        <v>0</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Deferred Tax Liability</t>
+          <t>Deferred Revenue - Non-Current</t>
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>15919</v>
+        <v>179788</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2249</v>
+        <v>171745</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2880</v>
+        <v>167227</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2201</v>
+        <v>164849</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2275</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="4" t="n">
-        <v>0</v>
+        <v>162471</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Long-Term Debt</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="4" t="n">
-        <v>862917</v>
-      </c>
-      <c r="J34" s="4" t="n">
-        <v>861472</v>
+          <t>Total Liabilities</t>
+        </is>
+      </c>
+      <c r="B34" s="6">
+        <f>B29+SUM(B30:B33)</f>
+        <v/>
+      </c>
+      <c r="C34" s="6">
+        <f>C29+SUM(C30:C33)</f>
+        <v/>
+      </c>
+      <c r="D34" s="6">
+        <f>D29+SUM(D30:D33)</f>
+        <v/>
+      </c>
+      <c r="E34" s="6">
+        <f>E29+SUM(E30:E33)</f>
+        <v/>
+      </c>
+      <c r="F34" s="6">
+        <f>F29+SUM(F30:F33)</f>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Deferred Revenue - Non-Current</t>
+          <t>Convertible Preferred Stock</t>
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>179788</v>
+        <v>824488</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>169370</v>
+        <v>824488</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>167227</v>
+        <v>824488</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>162471</v>
+        <v>824488</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>160092</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>157714</v>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>155336</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>156135</v>
-      </c>
-      <c r="J35" s="4" t="n">
-        <v>387432</v>
+        <v>824488</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Other Non-Current Liabilities</t>
+          <t>Common Stock</t>
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>2541</v>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>2574</v>
-      </c>
-      <c r="I36" s="4" t="n">
-        <v>25002</v>
-      </c>
-      <c r="J36" s="4" t="n">
-        <v>24431</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Total Liabilities</t>
-        </is>
-      </c>
-      <c r="B37" s="6">
-        <f>B30+SUM(B31:B36)</f>
-        <v/>
-      </c>
-      <c r="C37" s="6">
-        <f>C30+SUM(C31:C36)</f>
-        <v/>
-      </c>
-      <c r="D37" s="6">
-        <f>D30+SUM(D31:D36)</f>
-        <v/>
-      </c>
-      <c r="E37" s="6">
-        <f>E30+SUM(E31:E36)</f>
-        <v/>
-      </c>
-      <c r="F37" s="6">
-        <f>F30+SUM(F31:F36)</f>
-        <v/>
-      </c>
-      <c r="G37" s="6">
-        <f>G30+SUM(G31:G36)</f>
-        <v/>
-      </c>
-      <c r="H37" s="6">
-        <f>H30+SUM(H31:H36)</f>
-        <v/>
-      </c>
-      <c r="I37" s="6">
-        <f>I30+SUM(I31:I36)</f>
-        <v/>
-      </c>
-      <c r="J37" s="6">
-        <f>J30+SUM(J31:J36)</f>
-        <v/>
+          <t>Additional Paid-in Capital</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>280668</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>278980</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>276717</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>281247</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>286173</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Convertible Preferred Stock</t>
+          <t>Accumulated Other Comprehensive Income (Loss)</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>824488</v>
+        <v>-1881</v>
       </c>
       <c r="C38" s="4" t="n">
-        <v>824488</v>
+        <v>-1877</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>824488</v>
+        <v>-701</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>824488</v>
+        <v>-2055</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>824488</v>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>824488</v>
-      </c>
-      <c r="H38" s="4" t="n">
-        <v>824488</v>
-      </c>
-      <c r="I38" s="4" t="n">
-        <v>824488</v>
-      </c>
-      <c r="J38" s="4" t="n">
-        <v>1760275</v>
+        <v>-2363</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Common Stock</t>
+          <t>Retained Earnings (Accumulated Deficit)</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>76</v>
+        <v>-238772</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>77</v>
+        <v>-146118</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>77</v>
+        <v>-12053</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>78</v>
+        <v>58921</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>79</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>79</v>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>79</v>
-      </c>
-      <c r="I39" s="4" t="n">
-        <v>101</v>
-      </c>
-      <c r="J39" s="4" t="n">
-        <v>101</v>
+        <v>131866</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Additional Paid-in Capital</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>280668</v>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>277980</v>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>276717</v>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>286173</v>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>292576</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>297579</v>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>300877</v>
-      </c>
-      <c r="I40" s="4" t="n">
-        <v>1028384</v>
-      </c>
-      <c r="J40" s="4" t="n">
-        <v>1035021</v>
+          <t>Total Stockholders' Equity</t>
+        </is>
+      </c>
+      <c r="B40" s="6">
+        <f>SUM(B35:B39)</f>
+        <v/>
+      </c>
+      <c r="C40" s="6">
+        <f>SUM(C35:C39)</f>
+        <v/>
+      </c>
+      <c r="D40" s="6">
+        <f>SUM(D35:D39)</f>
+        <v/>
+      </c>
+      <c r="E40" s="6">
+        <f>SUM(E35:E39)</f>
+        <v/>
+      </c>
+      <c r="F40" s="6">
+        <f>SUM(F35:F39)</f>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Accumulated Other Comprehensive Income (Loss)</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="n">
-        <v>-1881</v>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>-2541</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>-701</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>-2363</v>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>-338</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>-3250</v>
-      </c>
-      <c r="H41" s="4" t="n">
-        <v>-1001</v>
-      </c>
-      <c r="I41" s="4" t="n">
-        <v>2178</v>
-      </c>
-      <c r="J41" s="4" t="n">
-        <v>2508</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Retained Earnings (Accumulated Deficit)</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n">
-        <v>-238772</v>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>-62169</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>-12053</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>131866</v>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>131309</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>105521</v>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>143159</v>
-      </c>
-      <c r="I42" s="4" t="n">
-        <v>236163</v>
-      </c>
-      <c r="J42" s="4" t="n">
-        <v>165480</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Total Stockholders' Equity</t>
-        </is>
-      </c>
-      <c r="B43" s="6">
-        <f>SUM(B38:B42)</f>
-        <v/>
-      </c>
-      <c r="C43" s="6">
-        <f>SUM(C38:C42)</f>
-        <v/>
-      </c>
-      <c r="D43" s="6">
-        <f>SUM(D38:D42)</f>
-        <v/>
-      </c>
-      <c r="E43" s="6">
-        <f>SUM(E38:E42)</f>
-        <v/>
-      </c>
-      <c r="F43" s="6">
-        <f>SUM(F38:F42)</f>
-        <v/>
-      </c>
-      <c r="G43" s="6">
-        <f>SUM(G38:G42)</f>
-        <v/>
-      </c>
-      <c r="H43" s="6">
-        <f>SUM(H38:H42)</f>
-        <v/>
-      </c>
-      <c r="I43" s="6">
-        <f>SUM(I38:I42)</f>
-        <v/>
-      </c>
-      <c r="J43" s="6">
-        <f>SUM(J38:J42)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
           <t>Total Liabilities, Mezzanine &amp; Stockholders' Equity</t>
         </is>
       </c>
-      <c r="B44" s="6">
-        <f>B37+B43</f>
-        <v/>
-      </c>
-      <c r="C44" s="6">
-        <f>C37+C43</f>
-        <v/>
-      </c>
-      <c r="D44" s="6">
-        <f>D37+D43</f>
-        <v/>
-      </c>
-      <c r="E44" s="6">
-        <f>E37+E43</f>
-        <v/>
-      </c>
-      <c r="F44" s="6">
-        <f>F37+F43</f>
-        <v/>
-      </c>
-      <c r="G44" s="6">
-        <f>G37+G43</f>
-        <v/>
-      </c>
-      <c r="H44" s="6">
-        <f>H37+H43</f>
-        <v/>
-      </c>
-      <c r="I44" s="6">
-        <f>I37+I43</f>
-        <v/>
-      </c>
-      <c r="J44" s="6">
-        <f>J37+J43</f>
+      <c r="B41" s="6">
+        <f>B34+B40</f>
+        <v/>
+      </c>
+      <c r="C41" s="6">
+        <f>C34+C40</f>
+        <v/>
+      </c>
+      <c r="D41" s="6">
+        <f>D34+D40</f>
+        <v/>
+      </c>
+      <c r="E41" s="6">
+        <f>E34+E40</f>
+        <v/>
+      </c>
+      <c r="F41" s="6">
+        <f>F34+F40</f>
         <v/>
       </c>
     </row>
@@ -6130,7 +5224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -6139,29 +5233,25 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr"/>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Q3 FY2022</t>
+          <t>Q2 FY2022</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>Q1 FY2023</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>Q2 FY2023</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Q3 FY2023</t>
-        </is>
-      </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Q1 FY2024</t>
@@ -6170,26 +5260,6 @@
       <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Q2 FY2024</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Q3 FY2024</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Q1 FY2025</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>Q2 FY2025</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>Q3 FY2025</t>
         </is>
       </c>
     </row>
@@ -6200,13 +5270,13 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>-166059</v>
+        <v>15838</v>
       </c>
       <c r="C2" s="4" t="n">
+        <v>41227</v>
+      </c>
+      <c r="D2" s="4" t="n">
         <v>92736</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>176685</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>77811</v>
@@ -6214,18 +5284,6 @@
       <c r="F2" s="4" t="n">
         <v>157594</v>
       </c>
-      <c r="G2" s="4" t="n">
-        <v>163950</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>44419</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>144274</v>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>83260</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -6234,30 +5292,18 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>952</v>
+        <v>556</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>1676</v>
+        <v>953</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6268,1494 +5314,720 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>402</v>
+        <v>275</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>445</v>
+        <v>294</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Impairment of Intangibles</t>
+          <t>Depreciation &amp; Amortization</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>2379</v>
+        <v>0</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0</v>
+        <v>549</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0</v>
+        <v>1229</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>0</v>
+        <v>2648</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Depreciation &amp; Amortization</t>
+          <t>Allowance for Credit Losses</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0</v>
+        <v>466</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1247</v>
+        <v>837</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0</v>
+        <v>1088</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1229</v>
+        <v>2250</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>2648</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>4888</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>2611</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>11730</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>20516</v>
+        <v>4072</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Allowance for Credit Losses</t>
+          <t>Amortization of Deferred Other Costs</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>705</v>
+        <v>0</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1088</v>
+        <v>3531</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1880</v>
+        <v>7062</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2250</v>
+        <v>3531</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4072</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>4279</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>2077</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>5529</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>3226</v>
+        <v>7062</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Amortization of Deferred Other Costs</t>
+          <t>Inventory Write-Down</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2354</v>
+        <v>331</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>7062</v>
+        <v>1672</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>10593</v>
+        <v>-3888</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>3531</v>
+        <v>2386</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>7062</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>10593</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>3531</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>7062</v>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>13391</v>
+        <v>11554</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Inventory Write-Down</t>
+          <t>Gain (Loss) on Disposal of PP&amp;E</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1078</v>
+        <v>0</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3888</v>
+        <v>0</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>2677</v>
+        <v>191</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2386</v>
+        <v>-8</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>11554</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>17118</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>5337</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>15262</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>22313</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Gain (Loss) on Disposal of PP&amp;E</t>
+          <t>Stock-Based Compensation</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>0</v>
+        <v>8517</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>191</v>
+        <v>5507</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>195</v>
+        <v>11242</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0</v>
+        <v>3563</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>126</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>0</v>
+        <v>8309</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Stock-Based Compensation</t>
+          <t>(Benefit) Provision for Deferred Income Taxes</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>14780</v>
+        <v>1072</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>11242</v>
+        <v>2873</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>16221</v>
+        <v>-41044</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3563</v>
+        <v>6450</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>8309</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>13685</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>5029</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>11463</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>18847</v>
+        <v>6112</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>(Benefit) Provision for Deferred Income Taxes</t>
+          <t>Foreign Currency Gain (Loss)</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>31329</v>
+        <v>602</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-41044</v>
+        <v>69</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-44303</v>
+        <v>206</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6450</v>
+        <v>369</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>6112</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>4727</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>269</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>-4161</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>-71408</v>
+        <v>633</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Foreign Currency Gain (Loss)</t>
+          <t>Accounts Receivable</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>1007</v>
+        <v>-27920</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>206</v>
+        <v>-109639</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>258</v>
+        <v>-135600</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0</v>
+        <v>-18664</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>633</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>356</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>0</v>
+        <v>-82213</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Change in Fair Value of Contingent Consideration</t>
+          <t>Inventories</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>0</v>
+        <v>28753</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0</v>
+        <v>17338</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0</v>
+        <v>24632</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0</v>
+        <v>29386</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>13800</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>13800</v>
+        <v>37052</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Other Operating Items</t>
+          <t>Prepaid Expenses</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>56</v>
+        <v>1257</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0</v>
+        <v>-4166</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2</v>
+        <v>-12058</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>361</v>
+        <v>-2076</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>-1014</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>-257</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>1964</v>
+        <v>-3469</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Accounts Receivable</t>
+          <t>Change in A/P and Accrued (legacy)</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>-78967</v>
+        <v>-7176</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-135600</v>
+        <v>0</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-153271</v>
+        <v>-12491</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-18664</v>
+        <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-82213</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>-26529</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>11841</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>-143153</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>-164133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Inventories</t>
+          <t>Accounts Payable</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>36211</v>
+        <v>0</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>24632</v>
+        <v>-19712</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-28092</v>
+        <v>0</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>29386</v>
+        <v>-3013</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>37052</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>14585</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>4794</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>23039</v>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v>31132</v>
+        <v>3950</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Prepaid Expenses</t>
+          <t>Accrued Expenses</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>1459</v>
+        <v>0</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-12058</v>
+        <v>12643</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-12406</v>
+        <v>0</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2076</v>
+        <v>1998</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-3469</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>-20261</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>-3687</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>-20645</v>
-      </c>
-      <c r="J18" s="4" t="n">
-        <v>-142920</v>
+        <v>17760</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Change in A/P and Accrued (legacy)</t>
+          <t>Other Current Liabilities</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>-3050</v>
+        <v>1820</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0</v>
+        <v>8759</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>14652</v>
+        <v>61128</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0</v>
+        <v>10344</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>0</v>
+        <v>-42094</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Other Non-Current Assets</t>
+          <t>Accrued Promotional Allowance</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>0</v>
+        <v>17512</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>8</v>
+        <v>32248</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0</v>
+        <v>62995</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-7695</v>
+        <v>29414</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-6362</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>-5303</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>-1552</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>-468</v>
-      </c>
-      <c r="J20" s="4" t="n">
-        <v>-275</v>
+        <v>56692</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Accounts Payable</t>
+          <t>Accrued Distributor Termination</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-10209</v>
+        <v>-2923</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0</v>
+        <v>-3986</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-3013</v>
+        <v>-248</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3950</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>-12259</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>11679</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>20789</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>4081</v>
+        <v>-248</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Accrued Expenses</t>
+          <t>ROU &amp; Lease Liability, Net</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>0</v>
+        <v>-95</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2282</v>
+        <v>-15</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0</v>
+        <v>-38</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1750</v>
+        <v>-23</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>17760</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>11151</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>-8673</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>-7013</v>
-      </c>
-      <c r="J22" s="4" t="n">
-        <v>32961</v>
+        <v>-34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Other Current Liabilities</t>
+          <t>Deferred Revenue</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>32590</v>
+        <v>0</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>61128</v>
+        <v>-4625</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>62901</v>
+        <v>-8219</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>10344</v>
+        <v>-2378</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-42094</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>-45537</v>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>13705</v>
-      </c>
-      <c r="I23" s="4" t="n">
-        <v>12927</v>
-      </c>
-      <c r="J23" s="4" t="n">
-        <v>42433</v>
+        <v>-4757</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Accrued Promotional Allowance</t>
+          <t>Other Operating Items</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>24213</v>
+        <v>0</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>62995</v>
+        <v>-4</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>100580</v>
+        <v>8</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>29414</v>
+        <v>-7672</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>56692</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>59023</v>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>15379</v>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>64221</v>
-      </c>
-      <c r="J24" s="4" t="n">
-        <v>83276</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Accrued Distributor Termination</t>
+          <t>Other Non-Current Assets</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>115551</v>
+        <v>488</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-3986</v>
+        <v>0</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-3986</v>
+        <v>0</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-248</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>-248</v>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="4" t="n">
-        <v>252953</v>
+        <v>-6362</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>ROU &amp; Lease Liability, Net</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="n">
-        <v>-126</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>-38</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>-64</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>-34</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v>0</v>
+          <t>Cash Flow from Operations</t>
+        </is>
+      </c>
+      <c r="B26" s="6">
+        <f>SUM(B2:B25)</f>
+        <v/>
+      </c>
+      <c r="C26" s="6">
+        <f>SUM(C2:C25)</f>
+        <v/>
+      </c>
+      <c r="D26" s="6">
+        <f>SUM(D2:D25)</f>
+        <v/>
+      </c>
+      <c r="E26" s="6">
+        <f>SUM(E2:E25)</f>
+        <v/>
+      </c>
+      <c r="F26" s="6">
+        <f>SUM(F2:F25)</f>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Deferred Revenue</t>
+          <t>Collections from Note Receivable</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>154103</v>
+        <v>2592</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-8219</v>
+        <v>3233</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-10593</v>
+        <v>3233</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-2378</v>
+        <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-4757</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>-7135</v>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>-2378</v>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>-7320</v>
-      </c>
-      <c r="J27" s="4" t="n">
-        <v>233463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Cash Flow from Operations</t>
-        </is>
-      </c>
-      <c r="B28" s="6">
-        <f>SUM(B2:B27)</f>
-        <v/>
-      </c>
-      <c r="C28" s="6">
-        <f>SUM(C2:C27)</f>
-        <v/>
-      </c>
-      <c r="D28" s="6">
-        <f>SUM(D2:D27)</f>
-        <v/>
-      </c>
-      <c r="E28" s="6">
-        <f>SUM(E2:E27)</f>
-        <v/>
-      </c>
-      <c r="F28" s="6">
-        <f>SUM(F2:F27)</f>
-        <v/>
-      </c>
-      <c r="G28" s="6">
-        <f>SUM(G2:G27)</f>
-        <v/>
-      </c>
-      <c r="H28" s="6">
-        <f>SUM(H2:H27)</f>
-        <v/>
-      </c>
-      <c r="I28" s="6">
-        <f>SUM(I2:I27)</f>
-        <v/>
-      </c>
-      <c r="J28" s="6">
-        <f>SUM(J2:J27)</f>
-        <v/>
+          <t>Purchase of PP&amp;E</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>-2456</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>-2253</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>-6810</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>-4525</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>-13739</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Collections from Note Receivable</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="n">
-        <v>2592</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>3233</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>3233</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="4" t="n">
-        <v>0</v>
+          <t>Cash Flow from Investing</t>
+        </is>
+      </c>
+      <c r="B29" s="6">
+        <f>SUM(B27:B28)</f>
+        <v/>
+      </c>
+      <c r="C29" s="6">
+        <f>SUM(C27:C28)</f>
+        <v/>
+      </c>
+      <c r="D29" s="6">
+        <f>SUM(D27:D28)</f>
+        <v/>
+      </c>
+      <c r="E29" s="6">
+        <f>SUM(E27:E28)</f>
+        <v/>
+      </c>
+      <c r="F29" s="6">
+        <f>SUM(F27:F28)</f>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Purchase of PP&amp;E</t>
+          <t>Finance Lease Payments</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>-3477</v>
+        <v>-37</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-6810</v>
+        <v>-11</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-12687</v>
+        <v>-22</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-4525</v>
+        <v>-15</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-13739</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>-17983</v>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>-6944</v>
-      </c>
-      <c r="I30" s="4" t="n">
-        <v>-15194</v>
-      </c>
-      <c r="J30" s="4" t="n">
-        <v>-25539</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Purchase of Non-Marketable Equity Securities</t>
+          <t>Proceeds from Exercise of Stock Options</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>0</v>
+        <v>1260</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0</v>
+        <v>478</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0</v>
+        <v>707</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0</v>
+        <v>967</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>-3000</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>-5000</v>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>-5000</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Acquisitions, Net of Cash Acquired</t>
+          <t>Preferred Dividends</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
         <v>0</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0</v>
+        <v>-6781</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0</v>
+        <v>-13637</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0</v>
+        <v>-6837</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>-1256351</v>
-      </c>
-      <c r="J32" s="4" t="n">
-        <v>-1278769</v>
+        <v>-13675</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Working Capital Estimate from Pepsi (Rockstar)</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="4" t="n">
-        <v>30617</v>
+          <t>Cash Flow from Financing</t>
+        </is>
+      </c>
+      <c r="B33" s="6">
+        <f>SUM(B30:B32)</f>
+        <v/>
+      </c>
+      <c r="C33" s="6">
+        <f>SUM(C30:C32)</f>
+        <v/>
+      </c>
+      <c r="D33" s="6">
+        <f>SUM(D30:D32)</f>
+        <v/>
+      </c>
+      <c r="E33" s="6">
+        <f>SUM(E30:E32)</f>
+        <v/>
+      </c>
+      <c r="F33" s="6">
+        <f>SUM(F30:F32)</f>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Cash Flow from Investing</t>
-        </is>
-      </c>
-      <c r="B34" s="6">
-        <f>SUM(B29:B33)</f>
-        <v/>
-      </c>
-      <c r="C34" s="6">
-        <f>SUM(C29:C33)</f>
-        <v/>
-      </c>
-      <c r="D34" s="6">
-        <f>SUM(D29:D33)</f>
-        <v/>
-      </c>
-      <c r="E34" s="6">
-        <f>SUM(E29:E33)</f>
-        <v/>
-      </c>
-      <c r="F34" s="6">
-        <f>SUM(F29:F33)</f>
-        <v/>
-      </c>
-      <c r="G34" s="6">
-        <f>SUM(G29:G33)</f>
-        <v/>
-      </c>
-      <c r="H34" s="6">
-        <f>SUM(H29:H33)</f>
-        <v/>
-      </c>
-      <c r="I34" s="6">
-        <f>SUM(I29:I33)</f>
-        <v/>
-      </c>
-      <c r="J34" s="6">
-        <f>SUM(J29:J33)</f>
-        <v/>
+          <t>FX Effect on Cash</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>121</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>-181</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>-555</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>-722</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>-766</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Finance Lease Payments</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="n">
-        <v>-49</v>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>-22</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>-33</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>-30</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>-46</v>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Proceeds from Exercise of Stock Options</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="n">
-        <v>3104</v>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>707</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>1603</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="4" t="n">
-        <v>1147</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>3832</v>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Proceeds from Issuance of Preferred Stock</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="n">
-        <v>542018</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Preferred Dividends</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="n">
-        <v>-4596</v>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>-13637</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>-20512</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>-6837</v>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>-13675</v>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>-20588</v>
-      </c>
-      <c r="H38" s="4" t="n">
-        <v>-6781</v>
-      </c>
-      <c r="I38" s="4" t="n">
-        <v>-13632</v>
-      </c>
-      <c r="J38" s="4" t="n">
-        <v>-23301</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Share Repurchases</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>-1658</v>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>-1932</v>
-      </c>
-      <c r="I39" s="4" t="n">
-        <v>-2811</v>
-      </c>
-      <c r="J39" s="4" t="n">
-        <v>-3259</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Proceeds from Issuance of Long-Term Debt</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="4" t="n">
-        <v>900000</v>
-      </c>
-      <c r="J40" s="4" t="n">
-        <v>900000</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Repayments of Long-Term Debt</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="4" t="n">
-        <v>-2250</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Debt Issuance Fees</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>-2195</v>
-      </c>
-      <c r="I42" s="4" t="n">
-        <v>-31581</v>
-      </c>
-      <c r="J42" s="4" t="n">
-        <v>-31581</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Other Financing Activities</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>952</v>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="4" t="n">
-        <v>321</v>
-      </c>
-      <c r="I43" s="4" t="n">
-        <v>319</v>
-      </c>
-      <c r="J43" s="4" t="n">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Cash Flow from Financing</t>
-        </is>
-      </c>
-      <c r="B44" s="6">
-        <f>SUM(B35:B43)</f>
-        <v/>
-      </c>
-      <c r="C44" s="6">
-        <f>SUM(C35:C43)</f>
-        <v/>
-      </c>
-      <c r="D44" s="6">
-        <f>SUM(D35:D43)</f>
-        <v/>
-      </c>
-      <c r="E44" s="6">
-        <f>SUM(E35:E43)</f>
-        <v/>
-      </c>
-      <c r="F44" s="6">
-        <f>SUM(F35:F43)</f>
-        <v/>
-      </c>
-      <c r="G44" s="6">
-        <f>SUM(G35:G43)</f>
-        <v/>
-      </c>
-      <c r="H44" s="6">
-        <f>SUM(H35:H43)</f>
-        <v/>
-      </c>
-      <c r="I44" s="6">
-        <f>SUM(I35:I43)</f>
-        <v/>
-      </c>
-      <c r="J44" s="6">
-        <f>SUM(J35:J43)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>FX Effect on Cash</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="n">
-        <v>158</v>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>-555</v>
-      </c>
-      <c r="D45" s="4" t="n">
-        <v>-555</v>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>-722</v>
-      </c>
-      <c r="F45" s="4" t="n">
-        <v>-766</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>-16</v>
-      </c>
-      <c r="H45" s="4" t="n">
-        <v>1259</v>
-      </c>
-      <c r="I45" s="4" t="n">
-        <v>2214</v>
-      </c>
-      <c r="J45" s="4" t="n">
-        <v>2174</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
           <t>Net Change in Cash</t>
         </is>
       </c>
-      <c r="B46" s="6">
-        <f>B28+B34+B44+B45</f>
-        <v/>
-      </c>
-      <c r="C46" s="6">
-        <f>C28+C34+C44+C45</f>
-        <v/>
-      </c>
-      <c r="D46" s="6">
-        <f>D28+D34+D44+D45</f>
-        <v/>
-      </c>
-      <c r="E46" s="6">
-        <f>E28+E34+E44+E45</f>
-        <v/>
-      </c>
-      <c r="F46" s="6">
-        <f>F28+F34+F44+F45</f>
-        <v/>
-      </c>
-      <c r="G46" s="6">
-        <f>G28+G34+G44+G45</f>
-        <v/>
-      </c>
-      <c r="H46" s="6">
-        <f>H28+H34+H44+H45</f>
-        <v/>
-      </c>
-      <c r="I46" s="6">
-        <f>I28+I34+I44+I45</f>
-        <v/>
-      </c>
-      <c r="J46" s="6">
-        <f>J28+J34+J44+J45</f>
+      <c r="B35" s="6">
+        <f>B26+B29+B33+B34</f>
+        <v/>
+      </c>
+      <c r="C35" s="6">
+        <f>C26+C29+C33+C34</f>
+        <v/>
+      </c>
+      <c r="D35" s="6">
+        <f>D26+D29+D33+D34</f>
+        <v/>
+      </c>
+      <c r="E35" s="6">
+        <f>E26+E29+E33+E34</f>
+        <v/>
+      </c>
+      <c r="F35" s="6">
+        <f>F26+F29+F33+F34</f>
         <v/>
       </c>
     </row>
